--- a/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 4,96</t>
+          <t>-15,07; 5,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 11,44</t>
+          <t>-9,9; 13,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 7,05</t>
+          <t>-15,25; 7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 3,41</t>
+          <t>-9,36; 2,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 14,16</t>
+          <t>-34,93; 17,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 34,83</t>
+          <t>-23,26; 42,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 26,97</t>
+          <t>-39,24; 28,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 3,79</t>
+          <t>-9,92; 3,06</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 10,58</t>
+          <t>-8,31; 9,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 12,65</t>
+          <t>-7,02; 11,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 10,52</t>
+          <t>-6,07; 10,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 8,37</t>
+          <t>-7,41; 8,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 32,91</t>
+          <t>-19,35; 29,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 42,74</t>
+          <t>-17,53; 37,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 40,69</t>
+          <t>-18,22; 40,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 10,31</t>
+          <t>-8,72; 10,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 10,88</t>
+          <t>-10,15; 10,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 6,81</t>
+          <t>-13,9; 6,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 5,72</t>
+          <t>-12,38; 5,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 9,38</t>
+          <t>-4,67; 8,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 37,34</t>
+          <t>-25,2; 36,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 22,26</t>
+          <t>-33,21; 22,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 17,37</t>
+          <t>-30,4; 16,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 11,26</t>
+          <t>-5,24; 10,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 9,63</t>
+          <t>-8,0; 8,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 11,94</t>
+          <t>-6,09; 11,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 9,66</t>
+          <t>-7,35; 10,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 2,15</t>
+          <t>-11,78; 3,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 31,43</t>
+          <t>-22,5; 31,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 55,38</t>
+          <t>-19,6; 47,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 34,24</t>
+          <t>-19,26; 37,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 2,62</t>
+          <t>-13,59; 3,86</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,04</t>
+          <t>-4,84; 4,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,82</t>
+          <t>-4,21; 5,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,3</t>
+          <t>-4,98; 3,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,36</t>
+          <t>-4,44; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 12,01</t>
+          <t>-12,89; 12,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 19,02</t>
+          <t>-11,82; 17,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 13,75</t>
+          <t>-14,32; 13,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,94</t>
+          <t>-5,08; 3,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 5,86</t>
+          <t>-15,06; 5,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 13,63</t>
+          <t>-11,89; 10,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 7,32</t>
+          <t>-15,56; 6,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 2,76</t>
+          <t>-8,92; 3,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 17,34</t>
+          <t>-35,58; 17,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 42,29</t>
+          <t>-27,34; 33,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 28,8</t>
+          <t>-40,64; 24,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 3,06</t>
+          <t>-9,47; 3,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 9,95</t>
+          <t>-8,57; 10,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 11,52</t>
+          <t>-6,15; 11,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 10,34</t>
+          <t>-7,15; 9,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 8,19</t>
+          <t>-7,36; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 29,42</t>
+          <t>-20,39; 31,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 37,95</t>
+          <t>-16,45; 37,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 40,37</t>
+          <t>-19,92; 35,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 10,16</t>
+          <t>-8,57; 10,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 10,45</t>
+          <t>-10,21; 9,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 6,7</t>
+          <t>-13,6; 6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 5,69</t>
+          <t>-12,68; 6,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,76</t>
+          <t>-4,7; 9,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 36,88</t>
+          <t>-26,24; 31,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 22,88</t>
+          <t>-33,19; 21,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 16,92</t>
+          <t>-31,21; 19,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 10,54</t>
+          <t>-5,26; 11,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 8,8</t>
+          <t>-7,93; 9,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 11,58</t>
+          <t>-6,91; 11,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 10,96</t>
+          <t>-7,4; 10,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 3,04</t>
+          <t>-11,45; 2,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 31,53</t>
+          <t>-20,86; 34,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 47,44</t>
+          <t>-20,85; 48,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 37,21</t>
+          <t>-18,76; 38,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 3,86</t>
+          <t>-13,13; 2,88</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,03</t>
+          <t>-4,91; 4,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,55</t>
+          <t>-4,1; 5,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,99</t>
+          <t>-5,32; 3,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,28</t>
+          <t>-4,2; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 12,07</t>
+          <t>-12,93; 13,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 17,6</t>
+          <t>-11,58; 17,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 13,0</t>
+          <t>-15,15; 12,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,87</t>
+          <t>-4,82; 3,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,27%</t>
+          <t>-2,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 5,77</t>
+          <t>-15,31; 4,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 10,8</t>
+          <t>-10,59; 11,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 6,49</t>
+          <t>-15,42; 7,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 3,17</t>
+          <t>-8,46; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 17,4</t>
+          <t>-35,55; 14,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 33,3</t>
+          <t>-24,57; 34,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 24,19</t>
+          <t>-39,99; 26,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 3,6</t>
+          <t>-8,9; 4,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 10,47</t>
+          <t>-8,31; 10,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 11,75</t>
+          <t>-6,34; 12,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 9,26</t>
+          <t>-6,94; 10,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 8,31</t>
+          <t>-2,39; 10,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 31,99</t>
+          <t>-19,93; 32,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 37,8</t>
+          <t>-16,29; 42,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 35,34</t>
+          <t>-20,5; 40,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 10,37</t>
+          <t>-2,77; 12,63</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 9,41</t>
+          <t>-9,98; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 6,41</t>
+          <t>-13,71; 6,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 6,36</t>
+          <t>-12,37; 5,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 9,65</t>
+          <t>-4,31; 8,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 31,34</t>
+          <t>-25,22; 37,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 21,97</t>
+          <t>-33,37; 22,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 19,45</t>
+          <t>-30,67; 17,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 11,6</t>
+          <t>-4,8; 10,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-3,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,51%</t>
+          <t>-3,65%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 9,84</t>
+          <t>-7,97; 9,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 11,71</t>
+          <t>-6,15; 11,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 10,64</t>
+          <t>-7,19; 9,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 2,33</t>
+          <t>-10,23; 3,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 34,11</t>
+          <t>-21,53; 31,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 48,24</t>
+          <t>-19,05; 55,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 38,64</t>
+          <t>-18,87; 34,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 2,88</t>
+          <t>-11,69; 4,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,48</t>
+          <t>-5,66; 4,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,45</t>
+          <t>-4,27; 5,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,91</t>
+          <t>-5,25; 4,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,3</t>
+          <t>-2,75; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,32</t>
+          <t>-14,66; 12,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,26</t>
+          <t>-11,83; 19,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 12,08</t>
+          <t>-14,77; 13,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,91</t>
+          <t>-3,11; 4,66</t>
         </is>
       </c>
     </row>
